--- a/光伏配储项目/电价数据/2026/庆核站.xlsx
+++ b/光伏配储项目/电价数据/2026/庆核站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.60197</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80415</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6777799999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6091299999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.59073</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.59069</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44039</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43566</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43262</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43499</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45663</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40846</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.20511</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.22016</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.18329</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20745</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06306</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24474</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24672</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23123</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.23238</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.9427300000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22888</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.53522</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5244500000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60058</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72536</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.20867</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.73756</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65389</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9275399999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53211</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.27038</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.38111</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.13929</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.23387</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34373</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.50391</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7474500000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.79904</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.30595</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12673</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86433</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7931699999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75309</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5142100000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47631</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42363</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6989099999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74012</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8608300000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.90112</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50593</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49577</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49596</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47866</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.67657</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5400900000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6382100000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.86303</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07782</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.94037</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.89425</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8504299999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.26276</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.06034</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5892000000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53972</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85776</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6034299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76591</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.82973</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.20659</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.76789</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15764</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87317</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.25774</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16223</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32111</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10325</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.14692</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70577</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.03743</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89205</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.04747</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9534400000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.07279</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87585</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44633</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81571</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83529</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44579</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42546</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33427</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5015500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48186</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46643</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.18721</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24528</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27234</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15573</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.56036</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.5021600000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.49629</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5896699999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.59615</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.67272</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.64088</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.91099</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7102000000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7828999999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8685499999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5216499999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5246000000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7748700000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72414</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6443300000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63878</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50036</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.5945199999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50413</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5120800000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5778799999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61251</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.58239</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.60436</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.22876</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.60891</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.73056</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51044</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57924</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71558</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7162200000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.85062</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45235</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59722</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45726</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54411</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.5996699999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.72809</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56211</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.86539</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6953400000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5794900000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51698</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64858</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43668</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34155</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51298</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49086</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43817</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46003</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6334099999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48539</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.97351</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5892200000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48837</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.63812</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53364</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6539400000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55011</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.51515</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50207</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47525</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45154</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30811</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24835</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26958</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.25126</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.24194</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23919</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22494</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08744</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.19119</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.15697</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01588</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44672</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.32903</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.20554</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.21662</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.23807</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10357</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01127</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2086</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19427</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.20764</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.02989</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06274</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06096</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32264</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.29845</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45183</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78489</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87095</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.69752</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.58823</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44857</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5574199999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6468200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.86782</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4891</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.68492</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.44278</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83112</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.49386</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57451</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33402</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90451</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19353</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27585</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.23436</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.25554</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27429</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.39069</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.25311</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.80065</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.37091</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.07105</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.64613</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.73473</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.59978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.21996</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24356</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14385</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26097</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.03172</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24463</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.47892</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6573300000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.26868</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27387</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.21446</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.22871</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.22401</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2055</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.19885</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.08142000000000001</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.21836</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.25862</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24336</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.21447</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15265</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.19626</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.21804</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24773</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22369</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26836</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24155</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24268</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26705</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22253</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23922</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24073</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22864</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26447</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24265</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30479</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23853</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.49951</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32433</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.21756</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.46358</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.74138</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.43605</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5461900000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5254099999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5640499999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48288</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.65291</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.82284</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.55843</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.5275</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.49566</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.65544</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.49294</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.50258</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.52525</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46311</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.54348</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68287</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48154</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.46317</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7422000000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48953</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.12883</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2428</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.23916</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24151</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.23853</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21312</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.23826</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24358</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25358</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23004</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.25928</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.27898</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27396</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32991</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6392599999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8070700000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.27167</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31316</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.43246</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.60334</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.55523</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6928</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.65027</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.71987</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84499</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.65739</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5584600000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5360499999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.52134</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.32998</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47013</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.46253</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.53473</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.60139</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6135900000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6846100000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8631799999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.4961</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.58323</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.48416</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.51498</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75428</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60619</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6528099999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.36895</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.12778</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.50888</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.04566</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.45545</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45957</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.26475</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27168</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.24586</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.22582</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.25787</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23414</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.22979</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.12796</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.11919</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.11834</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23006</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.11215</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.22899</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.11259</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.21659</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22254</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.21939</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22289</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.10893</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.22988</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.10845</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.09198000000000001</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.22862</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.20691</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24514</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.17962</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01525</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27276</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.23902</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22314</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.26625</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.14155</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23215</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.22854</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.09745000000000001</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.24775</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.12711</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.09068000000000001</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.09966</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.09965</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.09898999999999999</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23416</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.09815</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22222</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.09075</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.09065999999999999</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.10222</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.06537999999999999</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.10826</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00021</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14077</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01612</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04086</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04541</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00114</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03858</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02292</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03642</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19932</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26418</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.10076</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29714</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5132100000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.19416</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.23649</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22835</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23346</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23005</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.10275</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22538</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2111</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.10649</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.06895</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.08463</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.09642000000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.10957</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.07468999999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.12237</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.12869</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.14024</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26584</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.09606000000000001</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.54274</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86693</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85921</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10578</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09040999999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.17634</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.15953</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00117</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.06003</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6516000000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.54355</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.5854400000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.05767</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9730700000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.5529700000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.71727</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.60051</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8299299999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8281499999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83243</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9302699999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5416</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.5965499999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5495599999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33209</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45811</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48142</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.24899</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.22509</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.22847</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.10259</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.23891</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.53849</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.4749</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.31885</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.46438</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.69564</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.52461</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47198</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.6420399999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8461799999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.06503</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.47526</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.54144</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.57021</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.97326</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.88295</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.51937</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.63512</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41184</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.44146</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22098</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33771</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43206</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.42517</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5785800000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.19648</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.9821</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6387200000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.8407100000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51081</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.63009</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57217</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7795599999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.72437</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.97663</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.88173</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7897999999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.71154</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46153</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34219</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.12079</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.47926</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.73007</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21164</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.52015</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.72505</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.51205</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.6382100000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5026499999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47536</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6283200000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42217</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.34787</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.88862</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4626</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5201699999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.48528</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.48945</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.56686</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.47024</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46378</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35011</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17588</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14554</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19834</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12083</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22485</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26114</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14675</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19124</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22652</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.25984</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15419</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19554</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.13983</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.48694</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.52035</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37772</v>
       </c>
     </row>
   </sheetData>
